--- a/forecasting/DboFizLKolObs.xlsx
+++ b/forecasting/DboFizLKolObs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleks\OneDrive\Рабочий стол\НИР\Итог\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleks\PycharmProjects\NIR2\forecasting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9355B9BC-EE5A-47B9-A210-BB11C7143CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6916EFF1-30DB-4133-9F59-0EAF6334B876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16680" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="10572" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>I квартал 2021</t>
   </si>
@@ -94,6 +94,12 @@
   </si>
   <si>
     <t>III квартал  2025</t>
+  </si>
+  <si>
+    <t>IV квартал 2025</t>
+  </si>
+  <si>
+    <t>I квартал  2026</t>
   </si>
 </sst>
 </file>
@@ -654,13 +660,21 @@
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="2"/>
+      <c r="A20" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2">
+        <v>1394801</v>
+      </c>
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="2"/>
+      <c r="A21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2">
+        <v>494943</v>
+      </c>
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">

--- a/forecasting/DboFizLKolObs.xlsx
+++ b/forecasting/DboFizLKolObs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleks\PycharmProjects\NIR2\forecasting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6916EFF1-30DB-4133-9F59-0EAF6334B876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E1D456-DEB8-452E-BF5E-2441292F26A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="10572" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -663,8 +663,8 @@
       <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="2">
-        <v>1394801</v>
+      <c r="B20" s="7">
+        <v>109251</v>
       </c>
       <c r="C20" s="2"/>
     </row>
@@ -673,7 +673,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>494943</v>
+        <v>104309</v>
       </c>
       <c r="C21" s="2"/>
     </row>
